--- a/hotel.xlsx
+++ b/hotel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tasneem Meo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B18382-3DD8-48AF-9118-E00F68420AB0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678561B9-55A7-4F1E-BE17-DB21223231D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{5F13E190-1B77-417A-86F9-F64017B3F01C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="211">
   <si>
     <t>City</t>
   </si>
@@ -501,9 +501,6 @@
     <t>Razhek</t>
   </si>
   <si>
-    <t>4.9/6</t>
-  </si>
-  <si>
     <t>Shaheen Resort Hunza</t>
   </si>
   <si>
@@ -573,7 +570,94 @@
     <t>WiFi, Breakfast, Room Service</t>
   </si>
   <si>
-    <t>WiFi,  Room Service</t>
+    <t>Ramada Resort by Wyndham Murree</t>
+  </si>
+  <si>
+    <t>H077</t>
+  </si>
+  <si>
+    <t>H078</t>
+  </si>
+  <si>
+    <t>H079</t>
+  </si>
+  <si>
+    <t>H080</t>
+  </si>
+  <si>
+    <t>H081</t>
+  </si>
+  <si>
+    <t>H082</t>
+  </si>
+  <si>
+    <t>H084</t>
+  </si>
+  <si>
+    <t>H085</t>
+  </si>
+  <si>
+    <t>H086</t>
+  </si>
+  <si>
+    <t>H087</t>
+  </si>
+  <si>
+    <t>Murree</t>
+  </si>
+  <si>
+    <t>Skardu</t>
+  </si>
+  <si>
+    <t>4.5/4</t>
+  </si>
+  <si>
+    <t>On Cloud Resort</t>
+  </si>
+  <si>
+    <t>Fiora Hotel Murree</t>
+  </si>
+  <si>
+    <t>The Vibe by Ambience</t>
+  </si>
+  <si>
+    <t>Pinemount Hotel Murree</t>
+  </si>
+  <si>
+    <t>The Valley PentHouse</t>
+  </si>
+  <si>
+    <t>H088</t>
+  </si>
+  <si>
+    <t>H089</t>
+  </si>
+  <si>
+    <t>H090</t>
+  </si>
+  <si>
+    <t>PC Legacy Skardu</t>
+  </si>
+  <si>
+    <t>Broq Resort HussainAbad</t>
+  </si>
+  <si>
+    <t>Biafo Resort Skardu</t>
+  </si>
+  <si>
+    <t>Oasis Resort Katpana Sakardu</t>
+  </si>
+  <si>
+    <t>Arcadian Resort Skardu</t>
+  </si>
+  <si>
+    <t>Vantage Lodge Skardu</t>
+  </si>
+  <si>
+    <t>Safena Hotel Skardu</t>
+  </si>
+  <si>
+    <t>H091</t>
   </si>
 </sst>
 </file>
@@ -940,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7B5555-EFC1-48A6-A0E9-263DDF52BF86}">
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="4" width="22.36328125" customWidth="1"/>
@@ -964,13 +1048,13 @@
         <v>0</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>93</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>1</v>
@@ -979,16 +1063,16 @@
         <v>94</v>
       </c>
       <c r="I1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="K1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>168</v>
       </c>
       <c r="M1" s="4" t="s">
         <v>2</v>
@@ -1039,7 +1123,7 @@
         <v>95028</v>
       </c>
       <c r="N2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
@@ -1084,7 +1168,7 @@
         <v>135468</v>
       </c>
       <c r="N3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
@@ -1129,7 +1213,7 @@
         <v>55062</v>
       </c>
       <c r="N4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
@@ -1174,7 +1258,7 @@
         <v>60797</v>
       </c>
       <c r="N5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
@@ -1219,7 +1303,7 @@
         <v>60797</v>
       </c>
       <c r="N6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
@@ -1264,7 +1348,7 @@
         <v>30400</v>
       </c>
       <c r="N7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
@@ -1309,7 +1393,7 @@
         <v>18000</v>
       </c>
       <c r="N8" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
@@ -1354,7 +1438,7 @@
         <v>19200</v>
       </c>
       <c r="N9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
@@ -1399,7 +1483,7 @@
         <v>24000</v>
       </c>
       <c r="N10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
@@ -1444,7 +1528,7 @@
         <v>22800</v>
       </c>
       <c r="N11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
@@ -1489,7 +1573,7 @@
         <v>24000</v>
       </c>
       <c r="N12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
@@ -1534,7 +1618,7 @@
         <v>2100</v>
       </c>
       <c r="N13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
@@ -1579,7 +1663,7 @@
         <v>4200</v>
       </c>
       <c r="N14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
@@ -1624,7 +1708,7 @@
         <v>22800</v>
       </c>
       <c r="N15" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
@@ -1669,7 +1753,7 @@
         <v>7540</v>
       </c>
       <c r="N16" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
@@ -1714,7 +1798,7 @@
         <v>8420</v>
       </c>
       <c r="N17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
@@ -1759,7 +1843,7 @@
         <v>7120</v>
       </c>
       <c r="N18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
@@ -1804,7 +1888,7 @@
         <v>14440</v>
       </c>
       <c r="N19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
@@ -1849,7 +1933,7 @@
         <v>80000</v>
       </c>
       <c r="N20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
@@ -1894,7 +1978,7 @@
         <v>250000</v>
       </c>
       <c r="N21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
@@ -1939,7 +2023,7 @@
         <v>37700</v>
       </c>
       <c r="N22" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
@@ -1984,7 +2068,7 @@
         <v>22474</v>
       </c>
       <c r="N23" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
@@ -2029,7 +2113,7 @@
         <v>15302</v>
       </c>
       <c r="N24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
@@ -2074,7 +2158,7 @@
         <v>13500</v>
       </c>
       <c r="N25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
@@ -2119,7 +2203,7 @@
         <v>14500</v>
       </c>
       <c r="N26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
@@ -2164,7 +2248,7 @@
         <v>17900</v>
       </c>
       <c r="N27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
@@ -2209,7 +2293,7 @@
         <v>12000</v>
       </c>
       <c r="N28" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
@@ -2254,7 +2338,7 @@
         <v>5000</v>
       </c>
       <c r="N29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
@@ -2271,7 +2355,7 @@
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F30" t="s">
         <v>96</v>
@@ -2299,7 +2383,7 @@
         <v>6750</v>
       </c>
       <c r="N30" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
@@ -2344,7 +2428,7 @@
         <v>20880</v>
       </c>
       <c r="N31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
@@ -2389,7 +2473,7 @@
         <v>18241</v>
       </c>
       <c r="N32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
@@ -2434,7 +2518,7 @@
         <v>17972</v>
       </c>
       <c r="N33" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
@@ -2479,7 +2563,7 @@
         <v>2865</v>
       </c>
       <c r="N34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
@@ -2524,7 +2608,7 @@
         <v>52576</v>
       </c>
       <c r="N35" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
@@ -2569,7 +2653,7 @@
         <v>12528</v>
       </c>
       <c r="N36" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
@@ -2614,7 +2698,7 @@
         <v>30651</v>
       </c>
       <c r="N37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
@@ -2659,7 +2743,7 @@
         <v>46247</v>
       </c>
       <c r="N38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
@@ -2676,7 +2760,7 @@
         <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F39" t="s">
         <v>11</v>
@@ -2704,7 +2788,7 @@
         <v>40398</v>
       </c>
       <c r="N39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
@@ -2749,7 +2833,7 @@
         <v>17741</v>
       </c>
       <c r="N40" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.35">
@@ -2794,7 +2878,7 @@
         <v>22661</v>
       </c>
       <c r="N41" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
@@ -2839,7 +2923,7 @@
         <v>8084</v>
       </c>
       <c r="N42" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
@@ -2884,7 +2968,7 @@
         <v>29419</v>
       </c>
       <c r="N43" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
@@ -2929,7 +3013,7 @@
         <v>3345</v>
       </c>
       <c r="N44" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
@@ -2974,7 +3058,7 @@
         <v>14635</v>
       </c>
       <c r="N45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
@@ -3019,7 +3103,7 @@
         <v>14375</v>
       </c>
       <c r="N46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
@@ -3064,7 +3148,7 @@
         <v>36773</v>
       </c>
       <c r="N47" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
@@ -3109,7 +3193,7 @@
         <v>14347</v>
       </c>
       <c r="N48" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
@@ -3154,7 +3238,7 @@
         <v>7245</v>
       </c>
       <c r="N49" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
@@ -3199,7 +3283,7 @@
         <v>7130</v>
       </c>
       <c r="N50" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
@@ -3244,7 +3328,7 @@
         <v>13800</v>
       </c>
       <c r="N51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
@@ -3289,7 +3373,7 @@
         <v>68908</v>
       </c>
       <c r="N52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
@@ -3334,7 +3418,7 @@
         <v>35956</v>
       </c>
       <c r="N53" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
@@ -3379,7 +3463,7 @@
         <v>27700</v>
       </c>
       <c r="N54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
@@ -3424,7 +3508,7 @@
         <v>9500</v>
       </c>
       <c r="N55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
@@ -3469,7 +3553,7 @@
         <v>19433</v>
       </c>
       <c r="N56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
@@ -3514,7 +3598,7 @@
         <v>4933</v>
       </c>
       <c r="N57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
@@ -3559,7 +3643,7 @@
         <v>15750</v>
       </c>
       <c r="N58" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
@@ -3604,7 +3688,7 @@
         <v>21954</v>
       </c>
       <c r="N59" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
@@ -3627,7 +3711,7 @@
         <v>11</v>
       </c>
       <c r="G60" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="H60">
         <v>61</v>
@@ -3649,7 +3733,7 @@
         <v>46699</v>
       </c>
       <c r="N60" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
@@ -3666,13 +3750,13 @@
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F61" t="s">
         <v>96</v>
       </c>
       <c r="G61" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H61">
         <v>73</v>
@@ -3694,7 +3778,7 @@
         <v>11000</v>
       </c>
       <c r="N61" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
@@ -3739,7 +3823,7 @@
         <v>24264</v>
       </c>
       <c r="N62" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
@@ -3784,7 +3868,7 @@
         <v>82571</v>
       </c>
       <c r="N63" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
@@ -3829,7 +3913,7 @@
         <v>16000</v>
       </c>
       <c r="N64" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
@@ -3874,7 +3958,7 @@
         <v>27000</v>
       </c>
       <c r="N65" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
@@ -3919,7 +4003,7 @@
         <v>15109</v>
       </c>
       <c r="N66" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
@@ -3964,7 +4048,7 @@
         <v>28364</v>
       </c>
       <c r="N67" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
@@ -4009,7 +4093,7 @@
         <v>5574</v>
       </c>
       <c r="N68" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
@@ -4054,7 +4138,7 @@
         <v>64039</v>
       </c>
       <c r="N69" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
@@ -4071,7 +4155,7 @@
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F70" t="s">
         <v>96</v>
@@ -4099,7 +4183,7 @@
         <v>17160</v>
       </c>
       <c r="N70" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
@@ -4116,7 +4200,7 @@
         <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F71" t="s">
         <v>97</v>
@@ -4144,7 +4228,7 @@
         <v>42206</v>
       </c>
       <c r="N71" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
@@ -4161,7 +4245,7 @@
         <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F72" t="s">
         <v>11</v>
@@ -4189,7 +4273,7 @@
         <v>114400</v>
       </c>
       <c r="N72" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
@@ -4206,7 +4290,7 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F73" t="s">
         <v>96</v>
@@ -4234,7 +4318,7 @@
         <v>2475</v>
       </c>
       <c r="N73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
@@ -4279,7 +4363,7 @@
         <v>31631</v>
       </c>
       <c r="N74" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
@@ -4296,7 +4380,7 @@
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F75" t="s">
         <v>97</v>
@@ -4324,7 +4408,7 @@
         <v>21091</v>
       </c>
       <c r="N75" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
@@ -4341,7 +4425,7 @@
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F76" t="s">
         <v>97</v>
@@ -4369,7 +4453,7 @@
         <v>21120</v>
       </c>
       <c r="N76" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
@@ -4386,13 +4470,13 @@
         <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F77" t="s">
         <v>97</v>
       </c>
       <c r="G77" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H77">
         <v>175</v>
@@ -4410,11 +4494,686 @@
         <v>1</v>
       </c>
       <c r="M77">
-        <f t="shared" ref="M77" si="4">L77*K77</f>
+        <f t="shared" ref="M77:M92" si="4">L77*K77</f>
         <v>16500</v>
       </c>
       <c r="N77" t="s">
-        <v>178</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" t="s">
+        <v>8</v>
+      </c>
+      <c r="C78" t="s">
+        <v>192</v>
+      </c>
+      <c r="D78" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" t="s">
+        <v>181</v>
+      </c>
+      <c r="F78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78" t="s">
+        <v>194</v>
+      </c>
+      <c r="H78">
+        <v>1950</v>
+      </c>
+      <c r="I78">
+        <v>4</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="K78" s="1">
+        <v>42804</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <f t="shared" si="4"/>
+        <v>42804</v>
+      </c>
+      <c r="N78" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>183</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" t="s">
+        <v>192</v>
+      </c>
+      <c r="D79" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" t="s">
+        <v>195</v>
+      </c>
+      <c r="F79" t="s">
+        <v>96</v>
+      </c>
+      <c r="G79" t="s">
+        <v>103</v>
+      </c>
+      <c r="H79">
+        <v>100</v>
+      </c>
+      <c r="I79">
+        <v>3</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79" s="1">
+        <v>6472</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <f t="shared" si="4"/>
+        <v>6472</v>
+      </c>
+      <c r="N79" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>184</v>
+      </c>
+      <c r="B80" t="s">
+        <v>8</v>
+      </c>
+      <c r="C80" t="s">
+        <v>192</v>
+      </c>
+      <c r="D80" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" t="s">
+        <v>196</v>
+      </c>
+      <c r="F80" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" t="s">
+        <v>159</v>
+      </c>
+      <c r="H80">
+        <v>3700</v>
+      </c>
+      <c r="I80">
+        <v>3</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80" s="1">
+        <v>29077</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="M80">
+        <f t="shared" si="4"/>
+        <v>29077</v>
+      </c>
+      <c r="N80" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>185</v>
+      </c>
+      <c r="B81" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" t="s">
+        <v>192</v>
+      </c>
+      <c r="D81" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" t="s">
+        <v>197</v>
+      </c>
+      <c r="F81" t="s">
+        <v>97</v>
+      </c>
+      <c r="G81" t="s">
+        <v>105</v>
+      </c>
+      <c r="H81">
+        <v>315</v>
+      </c>
+      <c r="I81">
+        <v>3</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81" s="1">
+        <v>13835</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <f t="shared" si="4"/>
+        <v>13835</v>
+      </c>
+      <c r="N81" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>186</v>
+      </c>
+      <c r="B82" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" t="s">
+        <v>192</v>
+      </c>
+      <c r="D82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" t="s">
+        <v>96</v>
+      </c>
+      <c r="G82" t="s">
+        <v>105</v>
+      </c>
+      <c r="H82">
+        <v>280</v>
+      </c>
+      <c r="I82">
+        <v>3</v>
+      </c>
+      <c r="J82">
+        <v>4</v>
+      </c>
+      <c r="K82" s="1">
+        <v>12000</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <f t="shared" si="4"/>
+        <v>12000</v>
+      </c>
+      <c r="N82" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>187</v>
+      </c>
+      <c r="B83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" t="s">
+        <v>192</v>
+      </c>
+      <c r="D83" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" t="s">
+        <v>196</v>
+      </c>
+      <c r="F83" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" t="s">
+        <v>159</v>
+      </c>
+      <c r="H83">
+        <v>3700</v>
+      </c>
+      <c r="I83">
+        <v>3</v>
+      </c>
+      <c r="J83">
+        <v>4</v>
+      </c>
+      <c r="K83" s="1">
+        <v>35721</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <f t="shared" si="4"/>
+        <v>35721</v>
+      </c>
+      <c r="N83" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>188</v>
+      </c>
+      <c r="B84" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" t="s">
+        <v>192</v>
+      </c>
+      <c r="D84" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" t="s">
+        <v>199</v>
+      </c>
+      <c r="F84" t="s">
+        <v>97</v>
+      </c>
+      <c r="G84" t="s">
+        <v>159</v>
+      </c>
+      <c r="H84">
+        <v>12</v>
+      </c>
+      <c r="I84">
+        <v>3</v>
+      </c>
+      <c r="J84">
+        <v>4</v>
+      </c>
+      <c r="K84" s="1">
+        <v>26100</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <f t="shared" si="4"/>
+        <v>26100</v>
+      </c>
+      <c r="N84" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" t="s">
+        <v>193</v>
+      </c>
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>203</v>
+      </c>
+      <c r="F85" t="s">
+        <v>96</v>
+      </c>
+      <c r="G85" t="s">
+        <v>105</v>
+      </c>
+      <c r="H85">
+        <v>229</v>
+      </c>
+      <c r="I85">
+        <v>3</v>
+      </c>
+      <c r="J85">
+        <v>4</v>
+      </c>
+      <c r="K85" s="1">
+        <v>20821</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <f t="shared" si="4"/>
+        <v>20821</v>
+      </c>
+      <c r="N85" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>189</v>
+      </c>
+      <c r="B86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" t="s">
+        <v>193</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
+        <v>204</v>
+      </c>
+      <c r="F86" t="s">
+        <v>11</v>
+      </c>
+      <c r="G86" t="s">
+        <v>107</v>
+      </c>
+      <c r="H86">
+        <v>192</v>
+      </c>
+      <c r="I86">
+        <v>4</v>
+      </c>
+      <c r="J86">
+        <v>4</v>
+      </c>
+      <c r="K86" s="1">
+        <v>90000</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <f t="shared" si="4"/>
+        <v>90000</v>
+      </c>
+      <c r="N86" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>190</v>
+      </c>
+      <c r="B87" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" t="s">
+        <v>193</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" t="s">
+        <v>205</v>
+      </c>
+      <c r="F87" t="s">
+        <v>96</v>
+      </c>
+      <c r="G87" t="s">
+        <v>159</v>
+      </c>
+      <c r="H87">
+        <v>126</v>
+      </c>
+      <c r="I87">
+        <v>3</v>
+      </c>
+      <c r="J87">
+        <v>4</v>
+      </c>
+      <c r="K87" s="1">
+        <v>8800</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <f t="shared" si="4"/>
+        <v>8800</v>
+      </c>
+      <c r="N87" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>191</v>
+      </c>
+      <c r="B88" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" t="s">
+        <v>193</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" t="s">
+        <v>206</v>
+      </c>
+      <c r="F88" t="s">
+        <v>97</v>
+      </c>
+      <c r="G88" t="s">
+        <v>159</v>
+      </c>
+      <c r="H88">
+        <v>188</v>
+      </c>
+      <c r="I88">
+        <v>4</v>
+      </c>
+      <c r="J88">
+        <v>4</v>
+      </c>
+      <c r="K88" s="1">
+        <v>34000</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <f t="shared" si="4"/>
+        <v>34000</v>
+      </c>
+      <c r="N88" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>200</v>
+      </c>
+      <c r="B89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" t="s">
+        <v>193</v>
+      </c>
+      <c r="D89" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" t="s">
+        <v>207</v>
+      </c>
+      <c r="F89" t="s">
+        <v>97</v>
+      </c>
+      <c r="G89" t="s">
+        <v>113</v>
+      </c>
+      <c r="H89">
+        <v>511</v>
+      </c>
+      <c r="I89">
+        <v>4</v>
+      </c>
+      <c r="J89">
+        <v>2</v>
+      </c>
+      <c r="K89" s="1">
+        <v>14850</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89">
+        <f t="shared" si="4"/>
+        <v>14850</v>
+      </c>
+      <c r="N89" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>201</v>
+      </c>
+      <c r="B90" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" t="s">
+        <v>193</v>
+      </c>
+      <c r="D90" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" t="s">
+        <v>208</v>
+      </c>
+      <c r="F90" t="s">
+        <v>96</v>
+      </c>
+      <c r="G90" t="s">
+        <v>159</v>
+      </c>
+      <c r="H90">
+        <v>50</v>
+      </c>
+      <c r="I90">
+        <v>2</v>
+      </c>
+      <c r="J90">
+        <v>2</v>
+      </c>
+      <c r="K90" s="1">
+        <v>2767</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <f t="shared" si="4"/>
+        <v>2767</v>
+      </c>
+      <c r="N90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" t="s">
+        <v>193</v>
+      </c>
+      <c r="D91" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" t="s">
+        <v>209</v>
+      </c>
+      <c r="F91" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" t="s">
+        <v>159</v>
+      </c>
+      <c r="H91">
+        <v>61</v>
+      </c>
+      <c r="I91">
+        <v>3</v>
+      </c>
+      <c r="J91">
+        <v>2</v>
+      </c>
+      <c r="K91" s="1">
+        <v>12000</v>
+      </c>
+      <c r="L91">
+        <v>1</v>
+      </c>
+      <c r="M91">
+        <f t="shared" si="4"/>
+        <v>12000</v>
+      </c>
+      <c r="N91" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>210</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" t="s">
+        <v>193</v>
+      </c>
+      <c r="D92" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" t="s">
+        <v>206</v>
+      </c>
+      <c r="F92" t="s">
+        <v>97</v>
+      </c>
+      <c r="G92" t="s">
+        <v>159</v>
+      </c>
+      <c r="H92">
+        <v>188</v>
+      </c>
+      <c r="I92">
+        <v>4</v>
+      </c>
+      <c r="J92">
+        <v>2</v>
+      </c>
+      <c r="K92" s="1">
+        <v>17000</v>
+      </c>
+      <c r="L92">
+        <v>1</v>
+      </c>
+      <c r="M92">
+        <f t="shared" si="4"/>
+        <v>17000</v>
+      </c>
+      <c r="N92" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
